--- a/reports/pdf_change_20261020.xlsx
+++ b/reports/pdf_change_20261020.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,651억   ·   현금 208억(4.5%)      당일 2026-10-20  vs  전영업일 2026-10-19      매수 5종목  /  매도 8종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,644억      당일 2026-10-20  vs  전영업일 2026-10-19      매수 5종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>147</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1362079318</v>
+        <v>1366203795</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-144</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1297178758</v>
+        <v>-1301106711</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>38</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>965927252</v>
+        <v>968852151</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-61</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-855381253</v>
+        <v>-857971411</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>32</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1382642558</v>
+        <v>1386829302</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-50</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1330416882</v>
+        <v>-1334445483</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>31</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1433133985</v>
+        <v>1437473621</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-26</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-406329631</v>
+        <v>-407560028</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1379471360</v>
+        <v>1383648501</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-8</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1270857810</v>
+        <v>-1274706062</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>-7</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-855331703</v>
+        <v>-857921711</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>-4</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-765844445</v>
+        <v>-768163478</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>-3</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-832439614</v>
+        <v>-834960302</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,080억   ·   현금 60억(1.9%)      당일 2026-10-20  vs  전영업일 2026-10-19      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,166억      당일 2026-10-20  vs  전영업일 2026-10-19      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -991,7 +991,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,391억   ·   현금 40억(1.7%)      당일 2026-10-20  vs  전영업일 2026-10-19      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,403억      당일 2026-10-20  vs  전영업일 2026-10-19      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1015,7 +1015,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,004억   ·   현금 46억(2.2%)      당일 2026-10-20  vs  전영업일 2026-10-19      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,071억      당일 2026-10-20  vs  전영업일 2026-10-19      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1039,7 +1039,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 276억   ·   현금 3억(1.2%)      당일 2026-10-20  vs  전영업일 2026-10-19      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 282억      당일 2026-10-20  vs  전영업일 2026-10-19      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1176,11 +1176,11 @@
         <v>6</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>65927656</v>
+        <v>67303755</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>1.55%→1.62%</t>
+          <t>1.52%→1.59%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -1204,11 +1204,11 @@
         <v>3</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>103395081</v>
+        <v>107022978</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>3.38%→3.49%</t>
+          <t>3.37%→3.48%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -1225,7 +1225,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 828억   ·   현금 5억(0.6%)      당일 2026-10-20  vs  전영업일 2026-10-19      매수 2종목  /  매도 2종목</t>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 860억      당일 2026-10-20  vs  전영업일 2026-10-19      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1321,7 +1321,7 @@
         <v>163</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>319096826</v>
+        <v>335566552</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>-36</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-409571841</v>
+        <v>-430711306</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>90</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>221107414</v>
+        <v>232519557</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>-14</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-274938894</v>
+        <v>-289129471</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>1.67%→3.26%</t>
+          <t>1.67%→3.07%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>0.37%→1.04%</t>
+          <t>0.37%→1.05%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>1.53%→0.76%</t>
+          <t>1.53%→0.81%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -1579,23 +1579,23 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>큐리언트</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>213624000</v>
+        <v>35776000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>5.01%→5.36%</t>
+          <t>0.62%→0.63%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>27→31</t>
+          <t>20→24</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.35%</t>
+          <t>0.66%→0.37%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -1623,23 +1623,23 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>큐리언트</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>35776000</v>
+        <v>213624000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>0.62%→0.70%</t>
+          <t>5.01%→5.36%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>20→24</t>
+          <t>27→31</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>2.03%→0.87%</t>
+          <t>2.03%→0.84%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>0.74%→0.96%</t>
+          <t>0.74%→0.93%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -1702,11 +1702,11 @@
         <v>2</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>385280000</v>
+        <v>376250000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.22%</t>
+          <t>0.00%→1.19%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
